--- a/out/Attention-mamba2_repeat_5_000005.xlsx
+++ b/out/Attention-mamba2_repeat_5_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_5_000005.xlsx
+++ b/out/Attention-mamba2_repeat_5_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_5_000005.xlsx
+++ b/out/Attention-mamba2_repeat_5_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.4365603923797607</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.381554901599884</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.3609651625156403</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.3694822490215302</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.3184510469436646</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.3363182544708252</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.3535617887973785</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.2788625657558441</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.2249139845371246</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.2582454681396484</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.2389105558395386</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.2382327914237976</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.2159413695335388</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2521820366382599</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.2680386602878571</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.3603958487510681</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.3818196654319763</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.2073173224925995</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.3228355646133423</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1771572828292847</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.185052216053009</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.2577094435691833</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.1962204277515411</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.2408688962459564</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.1834526658058167</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2242110371589661</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2373911738395691</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.1896392405033112</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2195892333984375</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2470601797103882</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.1160406693816185</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2101121842861176</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.2325078248977661</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.2074582874774933</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.1669297814369202</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.2307146489620209</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.1686865091323853</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.1669432520866394</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.1929421722888947</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.1840274035930634</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.1908198595046997</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.1523771584033966</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.159680187702179</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.1845650970935822</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.1585068106651306</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.1687186062335968</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.1780993938446045</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.1592076420783997</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.1782196760177612</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.1619023382663727</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.1807608306407928</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.1633008122444153</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.169343501329422</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.1902706921100616</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.1781505644321442</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.2320573329925537</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.1890144348144531</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.2052879631519318</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.1923007369041443</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.1770513653755188</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.2053098380565643</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.1438171863555908</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.1617704331874847</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.1517479419708252</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.1508290767669678</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.1709663867950439</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.1546206772327423</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.1578966975212097</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.172021746635437</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.1606454253196716</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.1467153131961823</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.2000641226768494</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.2069548368453979</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.2574130892753601</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.2336326837539673</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.2592765092849731</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.2460260987281799</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.2240449786186218</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.2104082703590393</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.2070527076721191</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.2226194739341736</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.2215088605880737</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.2003026008605957</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.218986988067627</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.2023755311965942</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.2035970687866211</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.2359987199306488</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.2367062270641327</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.2158719003200531</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.1945297718048096</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.2034725546836853</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.1929709613323212</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.1899377703666687</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.2123349905014038</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.2160704135894775</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.2038315534591675</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.2020303010940552</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.200944721698761</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.1840090751647949</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.2116054594516754</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.2172754108905792</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.2051701545715332</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.2072433829307556</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.2223424315452576</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.2187834084033966</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.1959632337093353</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.218788743019104</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.1949043869972229</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.203643262386322</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.1782999336719513</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.190461665391922</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.2221466898918152</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.2455745339393616</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.272211492061615</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.2819214165210724</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.3175930976867676</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.2878887057304382</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.2794498205184937</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.2038961350917816</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.229989767074585</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.2665575742721558</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.2622087597846985</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.2260949611663818</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.2473442256450653</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.2397080063819885</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_5_000005.xlsx
+++ b/out/Attention-mamba2_repeat_5_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.4365603923797607</v>
+        <v>-0.4365602731704712</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.381554901599884</v>
+        <v>-0.3815546035766602</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.3609651625156403</v>
+        <v>-0.3609650433063507</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.3694822490215302</v>
+        <v>-0.3694820702075958</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.3184510469436646</v>
+        <v>-0.3184508681297302</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.3363182544708252</v>
+        <v>-0.336318165063858</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.3535617887973785</v>
+        <v>-0.3535616397857666</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.2788625657558441</v>
+        <v>-0.2788622975349426</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.2249139845371246</v>
+        <v>-0.2249137759208679</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.2582454681396484</v>
+        <v>-0.2582453489303589</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.2389105558395386</v>
+        <v>-0.2389102578163147</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.1199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.2382327914237976</v>
+        <v>-0.2382326424121857</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.1199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.2159413695335388</v>
+        <v>-0.2159415185451508</v>
       </c>
       <c r="JB14" t="n">
         <v>0.02000000000000007</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2521820366382599</v>
+        <v>-0.2521818578243256</v>
       </c>
       <c r="JB15" t="n">
         <v>0.02000000000000007</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.2680386602878571</v>
+        <v>-0.2680385112762451</v>
       </c>
       <c r="JB16" t="n">
         <v>0.02000000000000007</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.3603958487510681</v>
+        <v>-0.3603957295417786</v>
       </c>
       <c r="JB17" t="n">
         <v>0.02000000000000007</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.3818196654319763</v>
+        <v>-0.3818193972110748</v>
       </c>
       <c r="JB18" t="n">
         <v>0.02000000000000007</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.2073173224925995</v>
+        <v>-0.2073173522949219</v>
       </c>
       <c r="JB19" t="n">
         <v>0.1600000000000001</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.3228355646133423</v>
+        <v>-0.3228352665901184</v>
       </c>
       <c r="JB20" t="n">
         <v>0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1771572828292847</v>
+        <v>-0.1771569848060608</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.185052216053009</v>
+        <v>-0.1850519776344299</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.2577094435691833</v>
+        <v>-0.2577092349529266</v>
       </c>
       <c r="JB23" t="n">
         <v>0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.1962204277515411</v>
+        <v>-0.1962203085422516</v>
       </c>
       <c r="JB24" t="n">
         <v>0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.2408688962459564</v>
+        <v>-0.2408687174320221</v>
       </c>
       <c r="JB25" t="n">
         <v>0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.1834526658058167</v>
+        <v>-0.1834525763988495</v>
       </c>
       <c r="JB26" t="n">
         <v>0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2242110371589661</v>
+        <v>-0.2242110967636108</v>
       </c>
       <c r="JB27" t="n">
         <v>0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2373911738395691</v>
+        <v>-0.2373910546302795</v>
       </c>
       <c r="JB28" t="n">
         <v>0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.1896392405033112</v>
+        <v>-0.1896393001079559</v>
       </c>
       <c r="JB29" t="n">
         <v>0.1199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2195892333984375</v>
+        <v>-0.2195892632007599</v>
       </c>
       <c r="JB30" t="n">
         <v>0.2599999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.1160406693816185</v>
+        <v>-0.1160404309630394</v>
       </c>
       <c r="JB32" t="n">
         <v>0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2101121842861176</v>
+        <v>-0.2101119160652161</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.2325078248977661</v>
+        <v>-0.2325077056884766</v>
       </c>
       <c r="JB34" t="n">
         <v>0.8599999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.2074582874774933</v>
+        <v>-0.2074581980705261</v>
       </c>
       <c r="JB35" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.2307146489620209</v>
+        <v>-0.230714350938797</v>
       </c>
       <c r="JB37" t="n">
         <v>0.2599999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.1686865091323853</v>
+        <v>-0.1686864197254181</v>
       </c>
       <c r="JB38" t="n">
         <v>0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.1669432520866394</v>
+        <v>-0.1669432818889618</v>
       </c>
       <c r="JB39" t="n">
         <v>0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.1929421722888947</v>
+        <v>-0.1929421424865723</v>
       </c>
       <c r="JB40" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.1840274035930634</v>
+        <v>-0.1840271949768066</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.1908198595046997</v>
+        <v>-0.1908197402954102</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.1845650970935822</v>
+        <v>-0.184565007686615</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.1585068106651306</v>
+        <v>-0.1585067510604858</v>
       </c>
       <c r="JB46" t="n">
         <v>0.8599999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.1687186062335968</v>
+        <v>-0.1687185168266296</v>
       </c>
       <c r="JB47" t="n">
         <v>0.8599999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.1780993938446045</v>
+        <v>-0.1780993640422821</v>
       </c>
       <c r="JB48" t="n">
         <v>0.2599999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.1592076420783997</v>
+        <v>-0.159207671880722</v>
       </c>
       <c r="JB49" t="n">
         <v>0.1199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.1782196760177612</v>
+        <v>-0.1782197058200836</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.1619023382663727</v>
+        <v>-0.1619022786617279</v>
       </c>
       <c r="JB51" t="n">
         <v>0.1199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.1807608306407928</v>
+        <v>-0.1807608008384705</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.02000000000000007</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.1633008122444153</v>
+        <v>-0.1633007824420929</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.3</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.169343501329422</v>
+        <v>-0.1693434417247772</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.3</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.1902706921100616</v>
+        <v>-0.1902706623077393</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.4399999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.1781505644321442</v>
+        <v>-0.178150475025177</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.2320573329925537</v>
+        <v>-0.232057124376297</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.8599999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.2052879631519318</v>
+        <v>-0.2052878439426422</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.1923007369041443</v>
+        <v>-0.1923006474971771</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.2053098380565643</v>
+        <v>-0.2053097784519196</v>
       </c>
       <c r="JB62" t="n">
         <v>0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.1438171863555908</v>
+        <v>-0.1438171565532684</v>
       </c>
       <c r="JB63" t="n">
         <v>0.7199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.1617704331874847</v>
+        <v>-0.1617704033851624</v>
       </c>
       <c r="JB64" t="n">
         <v>0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.1508290767669678</v>
+        <v>-0.1508291065692902</v>
       </c>
       <c r="JB66" t="n">
         <v>0.8599999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.1709663867950439</v>
+        <v>-0.1709664762020111</v>
       </c>
       <c r="JB67" t="n">
         <v>0.8599999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.1546206772327423</v>
+        <v>-0.1546206474304199</v>
       </c>
       <c r="JB68" t="n">
         <v>0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.1578966975212097</v>
+        <v>-0.1578966677188873</v>
       </c>
       <c r="JB69" t="n">
         <v>0.5799999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.172021746635437</v>
+        <v>-0.1720216274261475</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.1606454253196716</v>
+        <v>-0.1606454849243164</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.16</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.2000641226768494</v>
+        <v>-0.2000641822814941</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.5799999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.2069548368453979</v>
+        <v>-0.2069546580314636</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.2574130892753601</v>
+        <v>-0.257412850856781</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.2336326837539673</v>
+        <v>-0.2336322665214539</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.2592765092849731</v>
+        <v>-0.2592763006687164</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.2460260987281799</v>
+        <v>-0.2460258603096008</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.2240449786186218</v>
+        <v>-0.2240447402000427</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.2104082703590393</v>
+        <v>-0.2104079723358154</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.2070527076721191</v>
+        <v>-0.2070525884628296</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.2226194739341736</v>
+        <v>-0.2226194143295288</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.2215088605880737</v>
+        <v>-0.2215085923671722</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.2003026008605957</v>
+        <v>-0.200302392244339</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.218986988067627</v>
+        <v>-0.2189866900444031</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.2023755311965942</v>
+        <v>-0.2023754417896271</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.2035970687866211</v>
+        <v>-0.2035969495773315</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.2359987199306488</v>
+        <v>-0.2359985709190369</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.2367062270641327</v>
+        <v>-0.2367059290409088</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.1199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.2158719003200531</v>
+        <v>-0.215871661901474</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.1199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.1945297718048096</v>
+        <v>-0.1945295929908752</v>
       </c>
       <c r="JB91" t="n">
         <v>0.1600000000000001</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.2034725546836853</v>
+        <v>-0.2034723460674286</v>
       </c>
       <c r="JB92" t="n">
         <v>0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.1929709613323212</v>
+        <v>-0.1929708421230316</v>
       </c>
       <c r="JB93" t="n">
         <v>0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.2123349905014038</v>
+        <v>-0.2123347222805023</v>
       </c>
       <c r="JB95" t="n">
         <v>0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.2160704135894775</v>
+        <v>-0.2160702347755432</v>
       </c>
       <c r="JB96" t="n">
         <v>0.16</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.2038315534591675</v>
+        <v>-0.2038314640522003</v>
       </c>
       <c r="JB97" t="n">
         <v>0.02000000000000007</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.2020303010940552</v>
+        <v>-0.2020300626754761</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.3</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.200944721698761</v>
+        <v>-0.2009445428848267</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.1840090751647949</v>
+        <v>-0.1840089559555054</v>
       </c>
       <c r="JB100" t="n">
         <v>0.3</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.2116054594516754</v>
+        <v>-0.211605429649353</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.2172754108905792</v>
+        <v>-0.2172751426696777</v>
       </c>
       <c r="JB102" t="n">
         <v>0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.2051701545715332</v>
+        <v>-0.2051699459552765</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.2072433829307556</v>
+        <v>-0.2072432339191437</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.2223424315452576</v>
+        <v>-0.2223422825336456</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.4399999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.2187834084033966</v>
+        <v>-0.2187831997871399</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.5799999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.1959632337093353</v>
+        <v>-0.1959629356861115</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.218788743019104</v>
+        <v>-0.2187885344028473</v>
       </c>
       <c r="JB108" t="n">
         <v>0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.1949043869972229</v>
+        <v>-0.194904088973999</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.203643262386322</v>
+        <v>-0.2036432921886444</v>
       </c>
       <c r="JB110" t="n">
         <v>0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.1782999336719513</v>
+        <v>-0.1782998144626617</v>
       </c>
       <c r="JB111" t="n">
         <v>0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.190461665391922</v>
+        <v>-0.1904615759849548</v>
       </c>
       <c r="JB112" t="n">
         <v>0.4399999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.2221466898918152</v>
+        <v>-0.222146600484848</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.2455745339393616</v>
+        <v>-0.2455742657184601</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.7199999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.272211492061615</v>
+        <v>-0.2722113728523254</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.2819214165210724</v>
+        <v>-0.2819211483001709</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.3175930976867676</v>
+        <v>-0.3175929486751556</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.2878887057304382</v>
+        <v>-0.2878884673118591</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.2794498205184937</v>
+        <v>-0.2794496119022369</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.2038961350917816</v>
+        <v>-0.2038959562778473</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.229989767074585</v>
+        <v>-0.2299896776676178</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.2665575742721558</v>
+        <v>-0.2665573954582214</v>
       </c>
       <c r="JB122" t="n">
         <v>0.02000000000000007</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.2622087597846985</v>
+        <v>-0.2622084021568298</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.2599999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.2473442256450653</v>
+        <v>-0.247344046831131</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.8599999999999997</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.2397080063819885</v>
+        <v>-0.2397079467773438</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.8599999999999997</v>
